--- a/output/pdf_financials_xlsx/VPT.xlsx
+++ b/output/pdf_financials_xlsx/VPT.xlsx
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.050831</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.023634</v>
@@ -2537,10 +2537,10 @@
         <v>0.013761</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.526026</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>9.268962999999999</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>5.18577</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.050831</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.023634</v>
@@ -2659,10 +2659,10 @@
         <v>0.013761</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.526026</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>9.268962999999999</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>5.18577</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.125106</v>
+        <v>0.07427499999999999</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.038303</v>
@@ -3391,10 +3391,10 @@
         <v>0.06378399999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.549154</v>
+        <v>0.023128</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.304834</v>
+        <v>0.035871</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.103487</v>
@@ -8068,25 +8068,25 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.046376</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013169</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.048866</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.050701</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.077902</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.084984</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.08852500000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8129,25 +8129,25 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.046376</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013169</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.048866</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.050701</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.077902</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.084984</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.08852500000000001</v>
       </c>
     </row>
     <row r="126">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -27826,7 +27826,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
@@ -30744,7 +30744,11 @@
           <t>Lease payments (Note 7)</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -33218,7 +33222,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -71708,7 +71716,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -73490,7 +73498,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">

--- a/output/pdf_financials_xlsx/VPT.xlsx
+++ b/output/pdf_financials_xlsx/VPT.xlsx
@@ -2206,25 +2206,25 @@
         <v>0.028285</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.024993</v>
+        <v>0.035325</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.019615</v>
+        <v>0.035325</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.013488</v>
+        <v>0.048812</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.041763</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.061243</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.06141</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>0.061242</v>
       </c>
     </row>
     <row r="29">
@@ -2267,25 +2267,25 @@
         <v>-2.055729</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.297635</v>
+        <v>-3.287303</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.831061</v>
+        <v>-1.815351</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.867542</v>
+        <v>-3.832218</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.8728</v>
+        <v>-4.831037</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.871937</v>
+        <v>-4.810694</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-5.003048</v>
+        <v>-4.941638</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-3.252448</v>
+        <v>-3.191206</v>
       </c>
     </row>
     <row r="30">
@@ -2334,10 +2334,10 @@
         <v>-3416.137394685677</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-4069.998642360811</v>
+        <v>-4057.246707724967</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-5083.879834522587</v>
+        <v>-5040.261543160174</v>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
@@ -2345,16 +2345,16 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-7148.326903046929</v>
+        <v>-7087.06118796485</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-9905.733688469592</v>
+        <v>-9781.213020759205</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-5256.848652965158</v>
+        <v>-5192.32337242046</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-1807.638610999955</v>
+        <v>-1773.601662887377</v>
       </c>
     </row>
     <row r="31">
@@ -6598,25 +6598,25 @@
         <v>0.028285</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0.024993</v>
+        <v>0.035325</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0.019615</v>
+        <v>0.035325</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0.013488</v>
+        <v>0.048812</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.041763</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.061243</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.06141</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.061242</v>
       </c>
     </row>
     <row r="101">
@@ -7315,7 +7315,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.001519</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -7324,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.000576</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -29400,7 +29400,11 @@
           <t>Depreciation of right-of-use asset (Note 7)</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -32094,7 +32098,11 @@
           <t>Depreciation of right of use asset</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -33948,7 +33956,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -41428,7 +41440,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -47618,7 +47634,11 @@
           <t>Loss on disposal of property and equipment 5</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -52454,7 +52474,11 @@
           <t>Loss on disposal of property and equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VPT.xlsx
+++ b/output/pdf_financials_xlsx/VPT.xlsx
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.02768</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>0</v>
@@ -2976,7 +2976,7 @@
         <v>0.285499</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0.251183</v>
+        <v>0.278863</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>0.132987</v>
@@ -3403,7 +3403,7 @@
         <v>0.056942</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.162567</v>
+        <v>0.134887</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>0.161221</v>
@@ -4388,13 +4388,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.264635</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.489824</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.588441</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -4409,10 +4409,10 @@
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.729124</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1.196048</v>
       </c>
       <c r="N64" s="3" t="n">
         <v>0</v>
@@ -4571,49 +4571,49 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.315622</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.43376</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.472229</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.415364</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.690898</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.680025</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.474232</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.100031</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.006817</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.159308</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.038906</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.098759</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.268381</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.210766</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.329186</v>
       </c>
     </row>
     <row r="68">
@@ -29296,7 +29296,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
